--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/American_Aircraft_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/American_Aircraft_Cumulative_Statistics_2020.xlsx
@@ -13,36 +13,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29" uniqueCount="29">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -124,11 +145,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
-    <col min="2" max="2" width="11.140625" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
     <col min="5" max="5" width="18.7109375" customWidth="true"/>
@@ -147,40 +168,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -188,40 +209,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2105665608</v>
+        <v>175524702</v>
       </c>
       <c r="C2" s="0">
-        <v>3646444020</v>
+        <v>276723315</v>
       </c>
       <c r="D2" s="0">
-        <v>373229</v>
+        <v>203473</v>
       </c>
       <c r="E2" s="0">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>24007</v>
+        <v>6734</v>
       </c>
       <c r="G2" s="0">
-        <v>2.46</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>6.7000000000000002</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="I2" s="0">
-        <v>57.75</v>
+        <v>63.43</v>
       </c>
       <c r="J2" s="0">
-        <v>1014</v>
+        <v>415</v>
       </c>
       <c r="K2" s="0">
-        <v>8146</v>
+        <v>2569.3600000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>54.380000000000003</v>
+        <v>25.949999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -229,40 +250,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>5455613437</v>
+        <v>8551173239</v>
       </c>
       <c r="C3" s="0">
-        <v>9079317309</v>
+        <v>12925053143</v>
       </c>
       <c r="D3" s="0">
-        <v>420728</v>
+        <v>309360</v>
       </c>
       <c r="E3" s="0">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="F3" s="0">
-        <v>56026</v>
+        <v>130326</v>
       </c>
       <c r="G3" s="0">
-        <v>2.6000000000000001</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>5.96</v>
+        <v>6.9299999999999997</v>
       </c>
       <c r="I3" s="0">
-        <v>60.090000000000003</v>
+        <v>66.159999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>892</v>
+        <v>775</v>
       </c>
       <c r="K3" s="0">
-        <v>3687</v>
+        <v>5192.6599999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>20.289999999999999</v>
+        <v>40.57</v>
       </c>
       <c r="M3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.11600000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -297,13 +318,13 @@
         <v>702</v>
       </c>
       <c r="K4" s="0">
-        <v>5483</v>
+        <v>5483.1999999999998</v>
       </c>
       <c r="L4" s="0">
         <v>36.549999999999997</v>
       </c>
       <c r="M4" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="5">
@@ -311,40 +332,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>3034945455</v>
+        <v>22327994188</v>
       </c>
       <c r="C5" s="0">
-        <v>5244076686</v>
+        <v>33622426310</v>
       </c>
       <c r="D5" s="0">
-        <v>285625</v>
+        <v>498184</v>
       </c>
       <c r="E5" s="0">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="F5" s="0">
-        <v>40220</v>
+        <v>155663</v>
       </c>
       <c r="G5" s="0">
-        <v>2.1899999999999999</v>
+        <v>2.3100000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>5.0099999999999998</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>57.869999999999997</v>
+        <v>66.409999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>831</v>
+        <v>1203</v>
       </c>
       <c r="K5" s="0">
-        <v>5043</v>
+        <v>7442.6899999999996</v>
       </c>
       <c r="L5" s="0">
-        <v>32.140000000000001</v>
+        <v>41.32</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="6">
@@ -352,40 +373,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>1902636192</v>
+        <v>2024901315</v>
       </c>
       <c r="C6" s="0">
-        <v>2702457522</v>
+        <v>3318175586</v>
       </c>
       <c r="D6" s="0">
-        <v>554919</v>
+        <v>539541</v>
       </c>
       <c r="E6" s="0">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F6" s="0">
-        <v>15013</v>
+        <v>11233</v>
       </c>
       <c r="G6" s="0">
-        <v>3.0800000000000001</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>8.1400000000000006</v>
+        <v>6.5800000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>70.400000000000006</v>
+        <v>61.020000000000003</v>
       </c>
       <c r="J6" s="0">
-        <v>992</v>
+        <v>1507</v>
       </c>
       <c r="K6" s="0">
-        <v>4753</v>
+        <v>9152.4300000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>26.210000000000001</v>
+        <v>46.700000000000003</v>
       </c>
       <c r="M6" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="7">
@@ -393,40 +414,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>9490770747</v>
+        <v>25068164783</v>
       </c>
       <c r="C7" s="0">
-        <v>16308869748</v>
+        <v>38225165222</v>
       </c>
       <c r="D7" s="0">
-        <v>341833</v>
+        <v>491074</v>
       </c>
       <c r="E7" s="0">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F7" s="0">
-        <v>86686</v>
+        <v>228352</v>
       </c>
       <c r="G7" s="0">
-        <v>1.8200000000000001</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>5.5099999999999998</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>58.189999999999998</v>
+        <v>65.579999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>1203</v>
+        <v>1008</v>
       </c>
       <c r="K7" s="0">
-        <v>5916</v>
+        <v>6713.5100000000002</v>
       </c>
       <c r="L7" s="0">
-        <v>37.829999999999998</v>
+        <v>40.439999999999998</v>
       </c>
       <c r="M7" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="8">
@@ -434,40 +455,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>8340000282</v>
+        <v>934888</v>
       </c>
       <c r="C8" s="0">
-        <v>12119394766</v>
+        <v>1131072</v>
       </c>
       <c r="D8" s="0">
-        <v>489080</v>
+        <v>1984</v>
       </c>
       <c r="E8" s="0">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F8" s="0">
-        <v>66671</v>
+        <v>6</v>
       </c>
       <c r="G8" s="0">
-        <v>2.6899999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H8" s="0">
-        <v>6.9800000000000004</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>68.819999999999993</v>
+        <v>82.659999999999997</v>
       </c>
       <c r="J8" s="0">
-        <v>993</v>
+        <v>1096</v>
       </c>
       <c r="K8" s="0">
-        <v>4110</v>
+        <v>16946.040000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>22.440000000000001</v>
+        <v>98.519999999999996</v>
       </c>
       <c r="M8" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="9">
@@ -475,40 +496,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>5307312233</v>
+        <v>1318720172</v>
       </c>
       <c r="C9" s="0">
-        <v>8254140900</v>
+        <v>1691175912</v>
       </c>
       <c r="D9" s="0">
-        <v>235228</v>
+        <v>748308</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F9" s="0">
-        <v>54811</v>
+        <v>6376</v>
       </c>
       <c r="G9" s="0">
-        <v>1.5600000000000001</v>
+        <v>2.8199999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>4.1500000000000004</v>
+        <v>10.35</v>
       </c>
       <c r="I9" s="0">
-        <v>64.299999999999997</v>
+        <v>77.980000000000004</v>
       </c>
       <c r="J9" s="0">
-        <v>1004</v>
+        <v>1484</v>
       </c>
       <c r="K9" s="0">
-        <v>5939</v>
+        <v>6188.6400000000003</v>
       </c>
       <c r="L9" s="0">
-        <v>39.600000000000001</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="M9" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="10">
@@ -516,40 +537,327 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>38840353469</v>
+        <v>791494012</v>
       </c>
       <c r="C10" s="0">
-        <v>62167519813</v>
+        <v>1004180561</v>
       </c>
       <c r="D10" s="0">
-        <v>357490</v>
+        <v>851000</v>
       </c>
       <c r="E10" s="0">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="F10" s="0">
-        <v>389141</v>
+        <v>2714</v>
       </c>
       <c r="G10" s="0">
-        <v>2.2400000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H10" s="0">
-        <v>5.7599999999999998</v>
+        <v>9.6500000000000004</v>
       </c>
       <c r="I10" s="0">
-        <v>62.479999999999997</v>
+        <v>78.819999999999993</v>
       </c>
       <c r="J10" s="0">
-        <v>977</v>
+        <v>1782</v>
       </c>
       <c r="K10" s="0">
-        <v>5300</v>
+        <v>7739.8699999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>32.450000000000003</v>
+        <v>37.240000000000002</v>
       </c>
       <c r="M10" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>764848906</v>
+      </c>
+      <c r="C11" s="0">
+        <v>1166931732</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1166932</v>
+      </c>
+      <c r="E11" s="0">
+        <v>245</v>
+      </c>
+      <c r="F11" s="0">
+        <v>2021</v>
+      </c>
+      <c r="G11" s="0">
+        <v>2.02</v>
+      </c>
+      <c r="H11" s="0">
+        <v>10.82</v>
+      </c>
+      <c r="I11" s="0">
+        <v>65.540000000000006</v>
+      </c>
+      <c r="J11" s="0">
+        <v>2369</v>
+      </c>
+      <c r="K11" s="0">
+        <v>9326.0799999999999</v>
+      </c>
+      <c r="L11" s="0">
+        <v>38.229999999999997</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.085999999999999993</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>580651821</v>
+      </c>
+      <c r="C12" s="0">
+        <v>848964049</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1543571</v>
+      </c>
+      <c r="E12" s="0">
+        <v>289</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1102</v>
+      </c>
+      <c r="G12" s="0">
+        <v>2</v>
+      </c>
+      <c r="H12" s="0">
+        <v>12</v>
+      </c>
+      <c r="I12" s="0">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="J12" s="0">
+        <v>2674</v>
+      </c>
+      <c r="K12" s="0">
+        <v>10717.059999999999</v>
+      </c>
+      <c r="L12" s="0">
+        <v>37.189999999999998</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.083000000000000004</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1902282145</v>
+      </c>
+      <c r="C13" s="0">
+        <v>4172843217</v>
+      </c>
+      <c r="D13" s="0">
+        <v>715754</v>
+      </c>
+      <c r="E13" s="0">
+        <v>228</v>
+      </c>
+      <c r="F13" s="0">
+        <v>5804</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0">
+        <v>6.5700000000000003</v>
+      </c>
+      <c r="I13" s="0">
+        <v>45.590000000000003</v>
+      </c>
+      <c r="J13" s="0">
+        <v>3211</v>
+      </c>
+      <c r="K13" s="0">
+        <v>12455.620000000001</v>
+      </c>
+      <c r="L13" s="0">
+        <v>55.549999999999997</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>2777905390</v>
+      </c>
+      <c r="C14" s="0">
+        <v>4643749866</v>
+      </c>
+      <c r="D14" s="0">
+        <v>792449</v>
+      </c>
+      <c r="E14" s="0">
+        <v>274</v>
+      </c>
+      <c r="F14" s="0">
+        <v>4376</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H14" s="0">
+        <v>6</v>
+      </c>
+      <c r="I14" s="0">
+        <v>59.82</v>
+      </c>
+      <c r="J14" s="0">
+        <v>3963</v>
+      </c>
+      <c r="K14" s="0">
+        <v>13424.540000000001</v>
+      </c>
+      <c r="L14" s="0">
+        <v>50.100000000000001</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>4873550032</v>
+      </c>
+      <c r="C15" s="0">
+        <v>7299087007</v>
+      </c>
+      <c r="D15" s="0">
+        <v>803864</v>
+      </c>
+      <c r="E15" s="0">
+        <v>266</v>
+      </c>
+      <c r="F15" s="0">
+        <v>8166</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="H15" s="0">
+        <v>6.3600000000000003</v>
+      </c>
+      <c r="I15" s="0">
+        <v>66.769999999999996</v>
+      </c>
+      <c r="J15" s="0">
+        <v>3389</v>
+      </c>
+      <c r="K15" s="0">
+        <v>12323.43</v>
+      </c>
+      <c r="L15" s="0">
+        <v>46.670000000000002</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.098000000000000004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>2700812565</v>
+      </c>
+      <c r="C16" s="0">
+        <v>5560102431</v>
+      </c>
+      <c r="D16" s="0">
+        <v>1222001</v>
+      </c>
+      <c r="E16" s="0">
+        <v>278</v>
+      </c>
+      <c r="F16" s="0">
+        <v>4809</v>
+      </c>
+      <c r="G16" s="0">
+        <v>1.0600000000000001</v>
+      </c>
+      <c r="H16" s="0">
+        <v>8.9299999999999997</v>
+      </c>
+      <c r="I16" s="0">
+        <v>48.57</v>
+      </c>
+      <c r="J16" s="0">
+        <v>4186</v>
+      </c>
+      <c r="K16" s="0">
+        <v>16069.91</v>
+      </c>
+      <c r="L16" s="0">
+        <v>58.149999999999999</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0">
+        <v>77062367673</v>
+      </c>
+      <c r="C17" s="0">
+        <v>119568528285</v>
+      </c>
+      <c r="D17" s="0">
+        <v>503998</v>
+      </c>
+      <c r="E17" s="0">
+        <v>165</v>
+      </c>
+      <c r="F17" s="0">
+        <v>613389</v>
+      </c>
+      <c r="G17" s="0">
+        <v>2.5899999999999999</v>
+      </c>
+      <c r="H17" s="0">
+        <v>7.3899999999999997</v>
+      </c>
+      <c r="I17" s="0">
+        <v>64.450000000000003</v>
+      </c>
+      <c r="J17" s="0">
+        <v>1102</v>
+      </c>
+      <c r="K17" s="0">
+        <v>7318.1599999999999</v>
+      </c>
+      <c r="L17" s="0">
+        <v>42.18</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0.107</v>
       </c>
     </row>
   </sheetData>
